--- a/education_forms/022_school_transport_survey--education_forms.xlsx
+++ b/education_forms/022_school_transport_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>school_transport_survey</t>
+          <t>School Transport Survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>school_transport_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>How often do students commute to school?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>school_transport_survey_category</t>
+          <t>school_transport_favourite_transportation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>school_transport_survey_category</t>
+          <t>What is their favorite mode of transport?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>school_transport_survey_description</t>
+          <t>school_transport_transportation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>school_transport_survey_description</t>
+          <t>Do students use a bus for transport?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>school_transport_survey_no_coding</t>
+          <t>school_transport_transportation_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>school_transport_survey_no_coding</t>
+          <t>Do students use a car for transport?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation</t>
+          <t>school_transport_transportation_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation</t>
+          <t>Do students walk to school?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency</t>
+          <t>school_transport_transportation_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency</t>
+          <t>Do students use a bike for transport?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency_2</t>
+          <t>school_transport_transportation_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency_2</t>
+          <t>Do students use other modes of transport?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency_3</t>
+          <t>school_transport_transportation_frequent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency_3</t>
+          <t>What mode of transport is used most frequently?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency_4</t>
+          <t>school_transport_transportation_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>school_transport_survey_frequency_4</t>
+          <t>How often do students use public transport?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_2</t>
+          <t>school_transport_transportation_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_2</t>
+          <t>What is the average travel time to school?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_3</t>
+          <t>school_transport_transportation_distance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_3</t>
+          <t>What is the average travel distance to school?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation</t>
+          <t>school_transport_survey_completed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation</t>
+          <t>Did the survey complete?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>school_transport_survey_survey_completed</t>
+          <t>school_transport_survey_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>school_transport_survey_survey_completed</t>
+          <t>How much time did the survey take?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>school_transport_survey_survey_time</t>
+          <t>school_transport_survey_date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>school_transport_survey_survey_time</t>
+          <t>What date was the survey completed?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>school_transport_survey_survey_date</t>
+          <t>school_transport_survey_staff</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>school_transport_survey_survey_date</t>
+          <t>Do students use school staff for transport?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>category_education</t>
+          <t>school_transport_survey_teacher</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>category_education</t>
+          <t>Do students use school teacher for transport?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>category_school_administration</t>
+          <t>school_transport_survey_parent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>category_school_administration</t>
+          <t>Do students use school parent for transport?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>category_school_staff</t>
+          <t>school_transport_survey_school_administration</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>category_school_staff</t>
+          <t>Do students use school administration for transport?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>category_parents</t>
+          <t>school_transport_survey_school_edition</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>category_parents</t>
+          <t>Do students use school education for transport?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,108 +980,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>category_teachers</t>
+          <t>school_transport_survey_transport</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>category_teachers</t>
+          <t>How many times do students take school transport per week?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>category_education</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>category_education</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>category_school_administration</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>category_school_administration</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>category_school_staff</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>category_school_staff</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>school_transport_survey_survey_completed_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>school_transport_survey_survey_completed_2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1126,272 +1034,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>school_transport_favourite_transportation_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bus</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>school_transport_favourite_transportation_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>school_transport_survey_category_choices</t>
+          <t>school_transport_favourite_transportation_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>walking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Walking</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>school_transport_survey_category_choices</t>
+          <t>school_transport_favourite_transportation_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bike</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_2_choices</t>
+          <t>school_transport_transportation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_2_choices</t>
+          <t>school_transport_transportation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_2_choices</t>
+          <t>school_transport_transportation_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_3_choices</t>
+          <t>school_transport_transportation_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_3_choices</t>
+          <t>school_transport_transportation_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>school_transport_survey_transportation_3_choices</t>
+          <t>school_transport_transportation_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>walking</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>walking</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation_choices</t>
+          <t>school_transport_transportation_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation_choices</t>
+          <t>school_transport_transportation_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation_choices</t>
+          <t>school_transport_transportation_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation_choices</t>
+          <t>school_transport_transportation_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation_choices</t>
+          <t>school_transport_transportation_frequent_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>walking</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>walking</t>
+          <t>Bus</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>school_transport_survey_favourite_transportation_choices</t>
+          <t>school_transport_transportation_frequent_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Car</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>school_transport_transportation_frequent_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>walking</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Walking</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>school_transport_transportation_frequent_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>school_transport_survey_staff_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>school_transport_survey_staff_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>school_transport_survey_teacher_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>school_transport_survey_teacher_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>school_transport_survey_parent_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>school_transport_survey_parent_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>school_transport_survey_school_administration_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>school_transport_survey_school_administration_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>school_transport_survey_school_edition_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>school_transport_survey_school_edition_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
